--- a/artfynd/A 62461-2025 artfynd.xlsx
+++ b/artfynd/A 62461-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128647139</v>
+        <v>128677192</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451138</v>
+        <v>450815</v>
       </c>
       <c r="R2" t="n">
-        <v>6710133</v>
+        <v>6709962</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,32 +746,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack runt hela trädet. Äldre</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,53 +776,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128646934</v>
+        <v>128677435</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451301</v>
+        <v>451297</v>
       </c>
       <c r="R3" t="n">
-        <v>6709989</v>
+        <v>6709993</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,32 +848,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128647292</v>
+        <v>128677423</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,37 +889,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451106</v>
+        <v>451295</v>
       </c>
       <c r="R4" t="n">
-        <v>6710134</v>
+        <v>6710006</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,32 +953,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Födohål</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128647015</v>
+        <v>128677168</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,46 +994,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451141</v>
+        <v>450878</v>
       </c>
       <c r="R5" t="n">
-        <v>6710113</v>
+        <v>6709947</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,27 +1054,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1137,14 +1084,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128677341</v>
+        <v>128677177</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1175,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451034</v>
+        <v>450862</v>
       </c>
       <c r="R6" t="n">
-        <v>6710184</v>
+        <v>6709947</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1238,42 +1185,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128678222</v>
+        <v>128677200</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,13 +1223,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450905</v>
+        <v>450805</v>
       </c>
       <c r="R7" t="n">
-        <v>6709951</v>
+        <v>6709970</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,32 +1256,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>kåda</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1358,14 +1286,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128677200</v>
+        <v>128677209</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1396,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450805</v>
+        <v>450780</v>
       </c>
       <c r="R8" t="n">
-        <v>6709970</v>
+        <v>6710010</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1459,38 +1387,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128677100</v>
+        <v>128677341</v>
       </c>
       <c r="B9" t="n">
-        <v>57725</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1498,13 +1425,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451158</v>
+        <v>451034</v>
       </c>
       <c r="R9" t="n">
-        <v>6710145</v>
+        <v>6710184</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,32 +1458,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>ringhack. Hela trädet</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1575,14 +1488,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128677209</v>
+        <v>128677346</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1613,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450780</v>
+        <v>451016</v>
       </c>
       <c r="R10" t="n">
-        <v>6710010</v>
+        <v>6710181</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128677238</v>
+        <v>128677350</v>
       </c>
       <c r="B11" t="n">
-        <v>78796</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>450787</v>
+        <v>451044</v>
       </c>
       <c r="R11" t="n">
-        <v>6710017</v>
+        <v>6710170</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,38 +1690,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128677435</v>
+        <v>128677354</v>
       </c>
       <c r="B12" t="n">
-        <v>96788</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1816,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451297</v>
+        <v>451032</v>
       </c>
       <c r="R12" t="n">
-        <v>6709993</v>
+        <v>6710168</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1879,14 +1791,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128677168</v>
+        <v>128677370</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1917,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450878</v>
+        <v>451143</v>
       </c>
       <c r="R13" t="n">
-        <v>6709947</v>
+        <v>6710142</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1980,14 +1892,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128677177</v>
+        <v>128677382</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2018,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450862</v>
+        <v>451175</v>
       </c>
       <c r="R14" t="n">
-        <v>6709947</v>
+        <v>6710145</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2081,14 +1993,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128677382</v>
+        <v>128677415</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2119,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451175</v>
+        <v>451284</v>
       </c>
       <c r="R15" t="n">
-        <v>6710145</v>
+        <v>6710055</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2182,62 +2094,51 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128647084</v>
+        <v>128677238</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451125</v>
+        <v>450787</v>
       </c>
       <c r="R16" t="n">
-        <v>6710158</v>
+        <v>6710017</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2264,27 +2165,18 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2303,51 +2195,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128677415</v>
+        <v>128646934</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451284</v>
+        <v>451301</v>
       </c>
       <c r="R17" t="n">
-        <v>6710055</v>
+        <v>6709989</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2374,18 +2268,32 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2404,51 +2312,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128677192</v>
+        <v>128647292</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450815</v>
+        <v>451106</v>
       </c>
       <c r="R18" t="n">
-        <v>6709962</v>
+        <v>6710134</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2475,18 +2380,32 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Födohål</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2505,55 +2424,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128677423</v>
+        <v>128647139</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451295</v>
+        <v>451138</v>
       </c>
       <c r="R19" t="n">
-        <v>6710006</v>
+        <v>6710133</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2580,18 +2497,32 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack runt hela trädet. Äldre</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2610,46 +2541,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128678087</v>
+        <v>128677068</v>
       </c>
       <c r="B20" t="n">
-        <v>56915</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2657,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450906</v>
+        <v>451030</v>
       </c>
       <c r="R20" t="n">
-        <v>6710013</v>
+        <v>6710094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,6 +2626,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>ringhack, Färska. Kåda synlig</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,10 +2657,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128677354</v>
+        <v>128677100</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2740,26 +2668,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2767,13 +2696,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451032</v>
+        <v>451158</v>
       </c>
       <c r="R21" t="n">
-        <v>6710168</v>
+        <v>6710145</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2800,18 +2729,32 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ringhack. Hela trädet</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2830,10 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128677346</v>
+        <v>128678222</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,26 +2784,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2868,13 +2816,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451016</v>
+        <v>450905</v>
       </c>
       <c r="R22" t="n">
-        <v>6710181</v>
+        <v>6709951</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2901,18 +2849,32 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>kåda</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2931,10 +2893,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128677395</v>
+        <v>128678328</v>
       </c>
       <c r="B23" t="n">
-        <v>78797</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,26 +2904,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2969,13 +2936,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451272</v>
+        <v>450904</v>
       </c>
       <c r="R23" t="n">
-        <v>6710087</v>
+        <v>6709926</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3002,18 +2969,32 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färskt</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3032,37 +3013,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128677370</v>
+        <v>128678087</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3070,13 +3060,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451143</v>
+        <v>450906</v>
       </c>
       <c r="R24" t="n">
-        <v>6710142</v>
+        <v>6710013</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3103,18 +3093,27 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3133,51 +3132,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128677350</v>
+        <v>128647015</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451044</v>
+        <v>451141</v>
       </c>
       <c r="R25" t="n">
-        <v>6710170</v>
+        <v>6710113</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3204,18 +3209,27 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3231,6 +3245,228 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128647084</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Blanktjärnen, Blanktjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>451125</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6710158</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128677395</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>451272</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6710087</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62461-2025 artfynd.xlsx
+++ b/artfynd/A 62461-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677168</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677177</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677200</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677209</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677341</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,6 +1631,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677346</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677350</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677354</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677370</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677382</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677415</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677238</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2309,6 +2389,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646934</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647292</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2538,6 +2628,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647139</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2654,6 +2749,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677068</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2770,6 +2870,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677100</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2890,6 +2995,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678222</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3010,6 +3120,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678328</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3129,6 +3244,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678087</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3245,6 +3365,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647015</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3366,6 +3491,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128647084</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3467,8 +3597,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128677395</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>